--- a/src/test/resources/tutorial/excluded-Header-Multi-Student.xlsx
+++ b/src/test/resources/tutorial/excluded-Header-Multi-Student.xlsx
@@ -90,7 +90,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n" s="6">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="3">
@@ -98,7 +98,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n" s="6">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
     </row>
   </sheetData>
